--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4057" uniqueCount="381">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -508,6 +508,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -697,6 +700,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -707,10 +713,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -723,6 +744,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -730,6 +760,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -737,6 +770,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -1110,6 +1146,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1486,7 +1528,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4525,7 +4567,9 @@
       <c r="K30" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L30" s="2"/>
+      <c r="L30" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4596,10 +4640,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4633,7 +4677,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>74</v>
@@ -4655,7 +4699,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>74</v>
@@ -4673,7 +4717,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4693,10 +4737,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4730,7 +4774,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>74</v>
@@ -4752,7 +4796,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4770,7 +4814,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4790,10 +4834,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4807,7 +4851,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4819,10 +4863,10 @@
         <v>95</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4873,7 +4917,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4893,10 +4937,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4910,7 +4954,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4919,13 +4963,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4976,7 +5020,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4996,10 +5040,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5097,10 +5141,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5116,7 +5160,7 @@
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5129,7 +5173,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5141,7 +5185,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -5180,7 +5224,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5200,17 +5244,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
@@ -5219,7 +5263,7 @@
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5232,7 +5276,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5244,7 +5288,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5283,7 +5327,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5303,17 +5347,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5335,7 +5379,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5347,7 +5391,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5386,7 +5430,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5406,17 +5450,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5438,7 +5482,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5489,7 +5533,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5509,17 +5553,17 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>75</v>
@@ -5528,7 +5572,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5541,7 +5585,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5553,7 +5597,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5592,7 +5636,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5612,10 +5656,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5638,11 +5682,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5693,7 +5737,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5713,10 +5757,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5743,7 +5787,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5794,7 +5838,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5814,17 +5858,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5842,11 +5886,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5897,7 +5941,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5917,17 +5961,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5945,11 +5989,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6000,7 +6044,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6020,17 +6064,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -6048,11 +6092,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6103,7 +6147,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6123,10 +6167,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6140,7 +6184,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6149,16 +6193,18 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -6206,7 +6252,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6226,10 +6272,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6243,7 +6289,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6252,15 +6298,17 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>74</v>
@@ -6309,7 +6357,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6329,10 +6377,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6355,12 +6403,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>74</v>
       </c>
@@ -6408,7 +6460,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6428,10 +6480,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6456,10 +6508,14 @@
       <c r="K49" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L49" s="2"/>
+      <c r="L49" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>74</v>
       </c>
@@ -6487,7 +6543,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6505,7 +6561,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6525,10 +6581,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6551,12 +6607,18 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>74</v>
       </c>
@@ -6604,7 +6666,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6624,10 +6686,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6650,12 +6712,14 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>74</v>
       </c>
@@ -6703,7 +6767,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6723,10 +6787,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6749,12 +6813,14 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -6802,7 +6868,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6822,10 +6888,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6839,7 +6905,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6848,7 +6914,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6889,7 +6955,7 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -6899,7 +6965,7 @@
         <v>124</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6919,13 +6985,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>74</v>
@@ -6947,7 +7013,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -7000,7 +7066,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7020,10 +7086,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7121,10 +7187,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7222,10 +7288,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7323,10 +7389,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7424,10 +7490,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7527,10 +7593,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7630,10 +7696,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7733,10 +7799,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7836,10 +7902,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7937,10 +8003,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7970,7 +8036,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
@@ -7996,7 +8062,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -8014,7 +8080,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8034,10 +8100,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8071,7 +8137,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -8113,7 +8179,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8133,10 +8199,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8159,7 +8225,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8212,7 +8278,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8232,10 +8298,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8258,7 +8324,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8311,7 +8377,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8331,10 +8397,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8357,7 +8423,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8410,7 +8476,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8430,10 +8496,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8456,7 +8522,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8509,7 +8575,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8529,10 +8595,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8555,7 +8621,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8608,7 +8674,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8628,10 +8694,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8654,10 +8720,10 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -8709,7 +8775,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8729,10 +8795,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8755,7 +8821,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8808,7 +8874,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8828,10 +8894,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8854,7 +8920,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8907,7 +8973,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8927,10 +8993,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8953,7 +9019,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -9006,7 +9072,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9026,13 +9092,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>74</v>
@@ -9054,7 +9120,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9107,7 +9173,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9127,10 +9193,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9228,10 +9294,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9329,10 +9395,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9430,10 +9496,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9531,10 +9597,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9634,10 +9700,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9737,10 +9803,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9840,10 +9906,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9943,10 +10009,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10044,10 +10110,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10077,7 +10143,7 @@
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
@@ -10103,7 +10169,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10121,7 +10187,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10141,10 +10207,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10178,7 +10244,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>74</v>
@@ -10220,7 +10286,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10240,10 +10306,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10266,10 +10332,10 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
@@ -10321,7 +10387,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10341,10 +10407,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10367,7 +10433,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10420,7 +10486,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10440,10 +10506,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10466,7 +10532,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10519,7 +10585,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10539,10 +10605,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10565,7 +10631,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10618,7 +10684,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10638,10 +10704,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10664,7 +10730,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10717,7 +10783,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10737,10 +10803,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10763,7 +10829,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10816,7 +10882,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10836,10 +10902,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10862,7 +10928,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10915,7 +10981,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10935,10 +11001,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10961,7 +11027,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11014,7 +11080,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11034,10 +11100,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11060,7 +11126,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11113,7 +11179,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11133,13 +11199,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>74</v>
@@ -11161,7 +11227,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11214,7 +11280,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11234,10 +11300,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11335,10 +11401,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11436,10 +11502,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11537,10 +11603,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11638,10 +11704,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11741,10 +11807,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11844,10 +11910,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11947,10 +12013,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12050,10 +12116,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12151,10 +12217,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12184,7 +12250,7 @@
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -12210,7 +12276,7 @@
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>74</v>
@@ -12228,7 +12294,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12248,10 +12314,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12285,7 +12351,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>74</v>
@@ -12327,7 +12393,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12347,10 +12413,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12373,7 +12439,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12426,7 +12492,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12446,10 +12512,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12472,7 +12538,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12525,7 +12591,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12545,10 +12611,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12571,10 +12637,10 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
@@ -12626,7 +12692,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12646,10 +12712,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12672,7 +12738,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12725,7 +12791,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12745,10 +12811,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12771,7 +12837,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12824,7 +12890,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12844,10 +12910,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12870,7 +12936,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -12923,7 +12989,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -12943,10 +13009,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12969,7 +13035,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13022,7 +13088,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13042,10 +13108,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13068,7 +13134,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13121,7 +13187,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13141,10 +13207,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13167,7 +13233,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13220,7 +13286,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13240,10 +13306,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13266,12 +13332,16 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="L117" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+      <c r="O117" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>74</v>
       </c>
@@ -13319,7 +13389,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13339,10 +13409,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13440,10 +13510,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13541,10 +13611,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13642,10 +13712,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13743,10 +13813,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13846,10 +13916,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13949,10 +14019,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14052,10 +14122,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14155,10 +14225,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14256,10 +14326,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14286,7 +14356,7 @@
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14295,7 +14365,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>74</v>
@@ -14337,7 +14407,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14357,10 +14427,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14394,7 +14464,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>74</v>
@@ -14436,7 +14506,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14456,10 +14526,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14482,7 +14552,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14535,7 +14605,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
